--- a/東広島市_安芸津・黒瀬エリア3蔵_主要日本酒一覧.xlsx
+++ b/東広島市_安芸津・黒瀬エリア3蔵_主要日本酒一覧.xlsx
@@ -8,12 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要銘柄" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選定基準" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド・中核銘柄" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要銘柄" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選定基準" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要銘柄'!$A$4:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'選定基準'!$A$4:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ブランド一覧'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ブランド・中核銘柄'!$A$4:$R$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'主要銘柄'!$A$4:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'選定基準'!$A$4:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -205,26 +209,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_752908" displayName="T_752908" ref="A4:J19" headerRowCount="1">
-  <autoFilter ref="A4:J19"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="酒蔵"/>
-    <tableColumn id="2" name="商品名"/>
-    <tableColumn id="3" name="分類"/>
-    <tableColumn id="4" name="甘辛目安"/>
-    <tableColumn id="5" name="日本酒度"/>
-    <tableColumn id="6" name="おすすめの飲み方"/>
-    <tableColumn id="7" name="容量"/>
-    <tableColumn id="8" name="流通区分"/>
-    <tableColumn id="9" name="選定理由"/>
-    <tableColumn id="10" name="出典URL"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_573163" displayName="T_573163" ref="A4:H10" headerRowCount="1">
+  <autoFilter ref="A4:H10"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="区分"/>
+    <tableColumn id="5" name="公式URL"/>
+    <tableColumn id="6" name="A中核銘柄数"/>
+    <tableColumn id="7" name="B主要銘柄数"/>
+    <tableColumn id="8" name="確認日"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_510675" displayName="T_510675" ref="A4:B9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_839278" displayName="T_839278" ref="A4:R25" headerRowCount="1">
+  <autoFilter ref="A4:R25"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="シリーズ"/>
+    <tableColumn id="5" name="中核銘柄"/>
+    <tableColumn id="6" name="優先度"/>
+    <tableColumn id="7" name="位置づけ"/>
+    <tableColumn id="8" name="ブランド収録判定"/>
+    <tableColumn id="9" name="個別SKU確認"/>
+    <tableColumn id="10" name="分類"/>
+    <tableColumn id="11" name="甘辛目安"/>
+    <tableColumn id="12" name="日本酒度"/>
+    <tableColumn id="13" name="おすすめの飲み方"/>
+    <tableColumn id="14" name="主要容量"/>
+    <tableColumn id="15" name="流通区分"/>
+    <tableColumn id="16" name="確認日"/>
+    <tableColumn id="17" name="根拠URL"/>
+    <tableColumn id="18" name="商品出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_565664" displayName="T_565664" ref="A4:M19" headerRowCount="1">
+  <autoFilter ref="A4:M19"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="酒蔵"/>
+    <tableColumn id="2" name="ブランド"/>
+    <tableColumn id="3" name="シリーズ"/>
+    <tableColumn id="4" name="商品名"/>
+    <tableColumn id="5" name="分類"/>
+    <tableColumn id="6" name="甘辛目安"/>
+    <tableColumn id="7" name="日本酒度"/>
+    <tableColumn id="8" name="おすすめの飲み方"/>
+    <tableColumn id="9" name="容量"/>
+    <tableColumn id="10" name="流通区分"/>
+    <tableColumn id="11" name="SKU確認"/>
+    <tableColumn id="12" name="選定理由"/>
+    <tableColumn id="13" name="出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_930275" displayName="T_930275" ref="A4:B9" headerRowCount="1">
   <autoFilter ref="A4:B9"/>
   <tableColumns count="2">
     <tableColumn id="1" name="基準"/>
@@ -650,849 +701,3316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>東広島市 安芸津・黒瀬エリア3蔵 主要日本酒一覧</t>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 ブランド一覧</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>各酒蔵 最大5商品。人気順位ではなく、現行流通・酒質の幅・公開情報の充実度を基準に選定。</t>
+          <t>主ブランド・別ブランド・主要シリーズを整理。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
           <t>酒蔵</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>ブランド</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>甘辛目安</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>日本酒度</t>
+          <t>公式URL</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>おすすめの飲み方</t>
+          <t>A中核銘柄数</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>容量</t>
+          <t>B主要銘柄数</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>流通区分</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>選定理由</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>出典URL</t>
+          <t>確認日</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>八反草 純米大吟醸</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
+          <t>賀茂金秀</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/daiginjo</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>八反草 純米吟醸</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>桜吹雪</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>別ブランド</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>辛口純米</t>
-        </is>
-      </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>辛口</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/karakuchi</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
           <t>今田酒造本店</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>FUKUCHO LEGACY I</t>
-        </is>
-      </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>FUKUCHO LEGACY</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
+          <t>海外・革新系シリーズ</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・その他枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/legacy1</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>今田酒造本店</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>山田錦 純米吟醸</t>
+          <t>柄酒造</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>9代目於多福</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>現行中心ブランド</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>https://fukucho.jp/products/yamadanishiki-junmaiginjo</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
           <t>柄酒造</t>
         </is>
       </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>従来主ブランド</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H10"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 ブランド・中核銘柄</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A＝絶対に落とさない代表・蔵元推奨等、B＝主要定番・高級・注目ライン。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>中核銘柄</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド収録判定</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>個別SKU確認</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>主要容量</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>根拠URL</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>商品出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸35</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>公式通年最高級ライン</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸40</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>公式通年純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米吟醸 雄町</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>公式通年・食との相性を訴求する代表銘柄</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>公式通年・「入魂の逸品」</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒（45～50℃）</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米 辛口</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>公式通年辛口ライン</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>9代目於多福 純米大吟醸 火入れ</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米13</t>
+        </is>
+      </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
+          <t>公式通年低アルコール系</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>冷酒（5～15℃前後）</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>https://j-s-p.or.jp/kuramoto/kanemitsu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>柄酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>於多福 大吟醸</t>
+          <t>金光酒造</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>大吟醸</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+          <t>桜吹雪</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>桜吹雪 特別純米うすにごり生</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>別ブランドの季節商品</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>1800ml</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/Limited/limited.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>柄酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>於多福 純米吟醸</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>八反草</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>富久長 八反草 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>公式が唯一醸す八反草の中心ライン</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 冷やして / 常温</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>柄酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>9代目於多福 特別純米 火入れ</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>特別純米</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
+          <t>海風土</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>富久長 海風土 Seafood 純米</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>公式が海風土シリーズを中心ラインとして訴求</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・特別純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-特別純米</t>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/seafood</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>柄酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>於多福 純米</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>富久長 純米吟醸 美穂 Biho</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>公式現行主要商品</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温 / 熱燗</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/biho</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>金光酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>賀茂金秀 純米大吟醸35</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>中口</t>
-        </is>
-      </c>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>富久長 辛口純米</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>冷酒（10～15℃前後）</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
+          <t>公式現行定番</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamokin.com/line_up/regular.html</t>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/karakuchi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>金光酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>賀茂金秀 純米吟醸 雄町</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>やや辛口</t>
+          <t>八反草</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>富久長 八反草 純米大吟醸 妙花風</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>冷酒（10～15℃前後）</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>公式トップおすすめ商品に掲載する八反草上位酒</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamokin.com/line_up/regular.html</t>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>金光酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>賀茂金秀 特別純米</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>特別純米</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>やや辛口</t>
+          <t>八反草 サタケシリーズ</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>富久長 八反草 サタケシリーズ HENPEI</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 燗酒（45～50℃）</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>公式おすすめ・サタケ精米シリーズ</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・特別純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamokin.com/line_up/regular.html</t>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattansohenpei</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>金光酒造</t>
+          <t>安芸津・黒瀬エリア3蔵</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>賀茂金秀 辛口特別純米</t>
+          <t>今田酒造本店</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>特別純米</t>
+          <t>富久長</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>辛口</t>
+          <t>白美</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>富久長 純米にごり スパークリング 白美 HAKUBI</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>冷酒（10～15℃前後）</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>現行スパークリング主要商品</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・特別純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamokin.com/line_up/regular.html</t>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hakubi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズの上位酒</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>於多福 大吟醸</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>従来主ブランドの上位定番</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>於多福 純米吟醸</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>従来主ブランドの主要商品</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 常温</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 特別純米</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-特別純米</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>安芸津・黒瀬エリア3蔵</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>於多福 一番取り</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>従来ブランド高級ライン</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/collections/all</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/関西一-一番取り-720ml</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:R25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 安芸津・黒瀬エリア3蔵 主要日本酒一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>各蔵Aランク5銘柄。売上順位ではなく、蔵元推奨・代表性・現行流通を優先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>容量</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>SKU確認</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>選定理由</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
           <t>金光酒造</t>
         </is>
       </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸35</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>公式通年最高級ライン</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米大吟醸40</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>公式通年純米大吟醸</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 純米吟醸 雄町</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>公式通年・食との相性を訴求する代表銘柄</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒（45～50℃）</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>公式通年・「入魂の逸品」</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>金光酒造</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂金秀 特別純米 辛口</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒（10～15℃前後）</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>公式通年辛口ライン</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamokin.com/line_up/regular.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>八反草</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>富久長 八反草 純米吟醸</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>公式が唯一醸す八反草の中心ライン</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/hattanso-junmaiginjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>海風土</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>富久長 海風土 Seafood 純米</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>公式が海風土シリーズを中心ラインとして訴求</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>富久長 純米吟醸 美穂 Biho</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>公式現行主要商品</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/biho</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>富久長 辛口純米</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>公式現行定番</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/karakuchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>今田酒造本店</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>富久長</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>八反草</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>富久長 八反草 純米大吟醸 妙花風</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>公式トップおすすめ商品に掲載する八反草上位酒</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>https://fukucho.jp/products/daiginjo_myokafu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米大吟醸</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズの上位酒</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米吟醸</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>9代目於多福 純米</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>現行中心シリーズ</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>於多福 大吟醸</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>従来主ブランドの上位定番</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-大吟醸-1800ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>柄酒造</t>
+        </is>
+      </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>賀茂金秀 純米大吟醸40</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
+          <t>於多福</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>中口</t>
+          <t>於多福 純米吟醸</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>純米吟醸</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>冷酒（10～15℃前後）</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 常温</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamokin.com/line_up/regular.html</t>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>従来主ブランドの主要商品</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tsukasyuzou.jp/products/於多福-純米吟醸-1800ml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J19"/>
+  <autoFilter ref="A4:M19"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -1501,7 +4019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/東広島市_安芸津・黒瀬エリア3蔵_主要日本酒一覧.xlsx
+++ b/東広島市_安芸津・黒瀬エリア3蔵_主要日本酒一覧.xlsx
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_573163" displayName="T_573163" ref="A4:H10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_515919" displayName="T_515919" ref="A4:H10" headerRowCount="1">
   <autoFilter ref="A4:H10"/>
   <tableColumns count="8">
     <tableColumn id="1" name="エリア"/>
@@ -226,7 +226,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_839278" displayName="T_839278" ref="A4:R25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_845705" displayName="T_845705" ref="A4:R25" headerRowCount="1">
   <autoFilter ref="A4:R25"/>
   <tableColumns count="18">
     <tableColumn id="1" name="エリア"/>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_565664" displayName="T_565664" ref="A4:M19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_726924" displayName="T_726924" ref="A4:M19" headerRowCount="1">
   <autoFilter ref="A4:M19"/>
   <tableColumns count="13">
     <tableColumn id="1" name="酒蔵"/>
@@ -275,7 +275,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_930275" displayName="T_930275" ref="A4:B9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_560804" displayName="T_560804" ref="A4:B9" headerRowCount="1">
   <autoFilter ref="A4:B9"/>
   <tableColumns count="2">
     <tableColumn id="1" name="基準"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q14" s="9" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q18" s="9" t="inlineStr">
@@ -2421,7 +2421,7 @@
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       <c r="L20" s="9" t="inlineStr"/>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温 / ロック</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="R20" s="9" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/9代目於多福-すずかぜ-720ml</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/火入れ-9代目於多福-純米大吟醸-720ml-1800ml</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       <c r="G16" s="9" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>冷酒 / 常温 / ロック</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>https://www.tsukasyuzou.jp/products/於多福-純米-1800ml</t>
+          <t>https://www.tsukasyuzou.jp/products/9代目於多福-すずかぜ-720ml</t>
         </is>
       </c>
     </row>
